--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,98 +434,98 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.08084</v>
+        <v>17.15659</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51437</v>
+        <v>17.09554</v>
       </c>
       <c r="E2" t="n">
-        <v>16.33859</v>
+        <v>17.14665</v>
       </c>
       <c r="F2" t="n">
-        <v>22.03997</v>
+        <v>42.99613</v>
       </c>
       <c r="G2" t="n">
-        <v>22.15233</v>
+        <v>0.05122</v>
       </c>
       <c r="H2" t="n">
-        <v>33.76523</v>
+        <v>1.81571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.93776</v>
+        <v>17.25399</v>
       </c>
       <c r="D3" t="n">
-        <v>15.8715</v>
+        <v>17.06258</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96324</v>
+        <v>17.11789</v>
       </c>
       <c r="F3" t="n">
-        <v>22.20103</v>
+        <v>42.73864</v>
       </c>
       <c r="G3" t="n">
-        <v>22.2473</v>
+        <v>0.05124</v>
       </c>
       <c r="H3" t="n">
-        <v>35.21639</v>
+        <v>1.83716</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.93467</v>
+        <v>16.89313</v>
       </c>
       <c r="D4" t="n">
-        <v>16.24699</v>
+        <v>16.60283</v>
       </c>
       <c r="E4" t="n">
-        <v>16.89053</v>
+        <v>16.76423</v>
       </c>
       <c r="F4" t="n">
-        <v>22.20886</v>
+        <v>43.43386</v>
       </c>
       <c r="G4" t="n">
-        <v>22.46755</v>
+        <v>0.05236</v>
       </c>
       <c r="H4" t="n">
-        <v>35.29229</v>
+        <v>1.88732</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.89989</v>
+        <v>17.04064</v>
       </c>
       <c r="D5" t="n">
-        <v>16.19659</v>
+        <v>16.84976</v>
       </c>
       <c r="E5" t="n">
-        <v>16.62471</v>
+        <v>16.93555</v>
       </c>
       <c r="F5" t="n">
-        <v>22.46447</v>
+        <v>42.91067</v>
       </c>
       <c r="G5" t="n">
-        <v>22.48666</v>
+        <v>0.05058</v>
       </c>
       <c r="H5" t="n">
-        <v>34.37589</v>
+        <v>1.82165</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.73689</v>
+        <v>17.0814</v>
       </c>
       <c r="D6" t="n">
-        <v>16.43954</v>
+        <v>16.77129</v>
       </c>
       <c r="E6" t="n">
-        <v>16.61046</v>
+        <v>16.92503</v>
       </c>
       <c r="F6" t="n">
-        <v>22.0623</v>
+        <v>43.44571</v>
       </c>
       <c r="G6" t="n">
-        <v>21.75141</v>
+        <v>0.05075</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3827</v>
+        <v>1.84893</v>
       </c>
     </row>
     <row r="7">
@@ -585,97 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.88034</v>
+        <v>17.40267</v>
       </c>
       <c r="D7" t="n">
-        <v>16.25895</v>
+        <v>16.84848</v>
       </c>
       <c r="E7" t="n">
-        <v>16.81165</v>
+        <v>16.96051</v>
       </c>
       <c r="F7" t="n">
-        <v>21.67954</v>
+        <v>43.57513</v>
       </c>
       <c r="G7" t="n">
-        <v>22.36018</v>
+        <v>0.05171</v>
       </c>
       <c r="H7" t="n">
-        <v>34.63612</v>
+        <v>1.88391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.56849</v>
+        <v>17.3481</v>
       </c>
       <c r="D8" t="n">
-        <v>16.32609</v>
+        <v>16.94302</v>
       </c>
       <c r="E8" t="n">
-        <v>16.61705</v>
+        <v>16.97077</v>
       </c>
       <c r="F8" t="n">
-        <v>22.33188</v>
+        <v>43.29168</v>
       </c>
       <c r="G8" t="n">
-        <v>22.61104</v>
+        <v>0.05192</v>
       </c>
       <c r="H8" t="n">
-        <v>35.05708</v>
+        <v>1.88579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.72533</v>
+        <v>17.10762</v>
       </c>
       <c r="D9" t="n">
-        <v>16.27843</v>
+        <v>16.92528</v>
       </c>
       <c r="E9" t="n">
-        <v>16.83499</v>
+        <v>17.03645</v>
       </c>
       <c r="F9" t="n">
-        <v>22.36825</v>
+        <v>43.67611</v>
       </c>
       <c r="G9" t="n">
-        <v>22.02895</v>
+        <v>0.05062</v>
       </c>
       <c r="H9" t="n">
-        <v>35.19297</v>
+        <v>1.89309</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17.21456</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16.7659</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.11549</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.23357</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05132</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.82523</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17.30586</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.84111</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.95175</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.84497</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.81656</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17.05863</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.68499</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.89456</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.91901</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05201</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.88733</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17.26459</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.76689</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.05568</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.88454</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05106</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.85886</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>17.10204</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17.00675</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.01795</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.48476</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.86045</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>17.08284</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.91002</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.08122</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.59645</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05134</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.85178</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>17.25548</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.60828</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.85994</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.2852</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05096</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.85964</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>17.25357</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.97873</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.25177</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.76602</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05228</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83957</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17.19459</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.8039</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.9567</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.49901</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05134</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.85191</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.17879</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.99324</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.99602</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.44347</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.82426</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17.32712</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17.05231</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.29823</v>
+      </c>
+      <c r="F20" t="n">
+        <v>43.7128</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05205</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.84692</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>17.0226</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.74594</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.98685</v>
+      </c>
+      <c r="F21" t="n">
+        <v>43.16276</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05082</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.85901</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>17.41389</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.82463</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.85018</v>
+      </c>
+      <c r="F22" t="n">
+        <v>43.69116</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.05189</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.82402</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>17.35329</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17.03169</v>
+      </c>
+      <c r="E23" t="n">
+        <v>17.08652</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42.67751</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.83588</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>17.17928</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16.87897</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.92946</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.95456</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05035</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.84936</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>17.08216</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16.56938</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.8937</v>
+      </c>
+      <c r="F25" t="n">
+        <v>43.26664</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.869</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>17.0813</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16.86162</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.87835</v>
+      </c>
+      <c r="F26" t="n">
+        <v>42.38775</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05047</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.85104</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>17.19734</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.60401</v>
+      </c>
+      <c r="E27" t="n">
+        <v>17.00691</v>
+      </c>
+      <c r="F27" t="n">
+        <v>42.72994</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.9013</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>17.2962</v>
+      </c>
+      <c r="D28" t="n">
+        <v>17.10662</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.18692</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.3032</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05136</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.8858</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>17.1473</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.84961</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.02566</v>
+      </c>
+      <c r="F29" t="n">
+        <v>44.06441</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.87204</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>17.38863</v>
+      </c>
+      <c r="D30" t="n">
+        <v>17.15079</v>
+      </c>
+      <c r="E30" t="n">
+        <v>17.16169</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.04218</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05121</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.86019</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17.1175</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.92838</v>
+      </c>
+      <c r="E31" t="n">
+        <v>17.08225</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42.96664</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05171</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.87005</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.3599</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17.07191</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.30354</v>
+      </c>
+      <c r="F32" t="n">
+        <v>42.78038</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.05269</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.87396</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.96865</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.81299</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.94406</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.88154</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05194</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.84875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.39822</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.72514</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.25361</v>
+      </c>
+      <c r="F34" t="n">
+        <v>43.89988</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.85773</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.27873</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.78178</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.9255</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.58805</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.83672</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.9942</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.71079</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.98883</v>
+      </c>
+      <c r="F36" t="n">
+        <v>43.18802</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05174</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.82614</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.18506</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.93744</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.12369</v>
+      </c>
+      <c r="F37" t="n">
+        <v>43.62463</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.8375</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17.01725</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.42028</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.57705</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.91553</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.34033</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.51405</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.57947</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.75043</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.13205</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.5506</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>16.95779</v>
-      </c>
-      <c r="D10" t="n">
-        <v>16.42154</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16.90503</v>
-      </c>
-      <c r="F10" t="n">
-        <v>21.95994</v>
-      </c>
-      <c r="G10" t="n">
-        <v>22.10956</v>
-      </c>
-      <c r="H10" t="n">
-        <v>34.87681</v>
+      <c r="C41" t="n">
+        <v>17.11159</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16.47988</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.61192</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22.2261</v>
+      </c>
+      <c r="G41" t="n">
+        <v>35.04997</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.83092</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.41558</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.81613</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.71134</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.40816</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.99386</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.42275</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.46796</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.07324</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.94821</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17.08093</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.4062</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.80765</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.63288</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.66453</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.02639</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.88678</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.37102</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.02966</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.9794</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.93402</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.51344</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.67495</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.21341</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.01117</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.66126</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.39179</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.59912</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.01588</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35.00362</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.06402</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.3883</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.76349</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.03228</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.78231</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.15936</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.19468</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.93237</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.93889</v>
+      </c>
+      <c r="G49" t="n">
+        <v>35.20898</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.83322</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.08524</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.80131</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.39669</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.40631</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>17.28182</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16.3489</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.70758</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22.59374</v>
+      </c>
+      <c r="G51" t="n">
+        <v>35.02264</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>17.12115</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.34199</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.43552</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.84749</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34.77596</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17.02384</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.18431</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.69637</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.80139</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34.89611</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17.2568</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.26974</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.67828</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22.01104</v>
+      </c>
+      <c r="G54" t="n">
+        <v>34.75985</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17.30755</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.14218</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.72154</v>
+      </c>
+      <c r="F55" t="n">
+        <v>21.48287</v>
+      </c>
+      <c r="G55" t="n">
+        <v>35.25579</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.84922</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.09986</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.63194</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.9316</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.70018</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.79974</v>
+      </c>
+      <c r="D57" t="n">
+        <v>15.89984</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.68501</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22.38641</v>
+      </c>
+      <c r="G57" t="n">
+        <v>35.6247</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.89264</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.36554</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.82528</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22.5987</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.54525</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.92248</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.35507</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.65789</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22.39255</v>
+      </c>
+      <c r="G59" t="n">
+        <v>34.73269</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>17.31597</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.27956</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.48495</v>
+      </c>
+      <c r="F60" t="n">
+        <v>22.27095</v>
+      </c>
+      <c r="G60" t="n">
+        <v>35.11959</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16.78702</v>
+      </c>
+      <c r="D61" t="n">
+        <v>16.04593</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.77627</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22.08978</v>
+      </c>
+      <c r="G61" t="n">
+        <v>35.30074</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>16.9724</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15.97998</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.59534</v>
+      </c>
+      <c r="F62" t="n">
+        <v>21.98772</v>
+      </c>
+      <c r="G62" t="n">
+        <v>35.30268</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>17.09995</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16.2401</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.40911</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22.05615</v>
+      </c>
+      <c r="G63" t="n">
+        <v>34.59765</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>16.96979</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16.43276</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.62017</v>
+      </c>
+      <c r="F64" t="n">
+        <v>22.2485</v>
+      </c>
+      <c r="G64" t="n">
+        <v>35.20715</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>17.05969</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16.03149</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.83483</v>
+      </c>
+      <c r="F65" t="n">
+        <v>22.02589</v>
+      </c>
+      <c r="G65" t="n">
+        <v>34.7155</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>17.16115</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.23066</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.82157</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22.03098</v>
+      </c>
+      <c r="G66" t="n">
+        <v>33.83401</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>17.12019</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16.35807</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.58801</v>
+      </c>
+      <c r="F67" t="n">
+        <v>22.53354</v>
+      </c>
+      <c r="G67" t="n">
+        <v>34.99762</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>17.00512</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.18965</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.44003</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22.06403</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.30194</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>16.9306</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16.25964</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.68064</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.88375</v>
+      </c>
+      <c r="G69" t="n">
+        <v>34.19579</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>16.77137</v>
+      </c>
+      <c r="D70" t="n">
+        <v>16.30481</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.6632</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.76279</v>
+      </c>
+      <c r="G70" t="n">
+        <v>34.66248</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>16.94825</v>
+      </c>
+      <c r="D71" t="n">
+        <v>15.97113</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.51299</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.95536</v>
+      </c>
+      <c r="G71" t="n">
+        <v>35.40432</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.93583</v>
+      </c>
+      <c r="D72" t="n">
+        <v>16.58776</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.82625</v>
+      </c>
+      <c r="F72" t="n">
+        <v>22.30354</v>
+      </c>
+      <c r="G72" t="n">
+        <v>34.50571</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.82736</v>
+      </c>
+      <c r="D73" t="n">
+        <v>16.55232</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.72996</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.8957</v>
+      </c>
+      <c r="G73" t="n">
+        <v>35.08352</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>17.05552</v>
+      </c>
+      <c r="D74" t="n">
+        <v>16.37672</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.49578</v>
+      </c>
+      <c r="F74" t="n">
+        <v>22.22213</v>
+      </c>
+      <c r="G74" t="n">
+        <v>35.25213</v>
       </c>
     </row>
   </sheetData>
